--- a/WorkBot/main/data/order_archive/Performance Food/Performance Food_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Performance Food/Performance Food_Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,972 @@
         <v>34.79</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FC576</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Oil - Olive Extra Virgin</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="E26" t="n">
+        <v>340.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FA300</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sundried Tomatoes</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="E27" t="n">
+        <v>126.35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L6434</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="E28" t="n">
+        <v>82.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>81692</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Can - Garbanzo Beans</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="E29" t="n">
+        <v>95.04000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CV664</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pasta - Elbow</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25.74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CV630</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pasta - Rotini (Tricolor)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>25204</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rice - Long Grain (Parboiled)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>24.55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>22216</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tuna White Chunk (Pouch)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>74</v>
+      </c>
+      <c r="E33" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>K1570</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Buttermilk</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>18.38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CF096</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fresh Mozz (Sliced)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100.38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>42902</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bacon Thick Cut (Smoked)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>210.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JP006</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chicken Breast (6oz)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>164.98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GC898</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chicken Breast - Random</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="E38" t="n">
+        <v>264.09</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WF580</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Corned Beef (Sliced)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>213.63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HH264</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Muenster (Sliced)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="E40" t="n">
+        <v>192.28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>E3556</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pastrami (Sliced)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>274.28</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RC608</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PKT Sour Cream</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>36776</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Prosciutto</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="E43" t="n">
+        <v>124.96</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NH016</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Provolone (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="E44" t="n">
+        <v>322.92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>83632</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Roast Beef (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>130.56</v>
+      </c>
+      <c r="E45" t="n">
+        <v>652.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>38476</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Salami (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>75104</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cantaloupe - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>76.41</v>
+      </c>
+      <c r="E47" t="n">
+        <v>229.23</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>G5204</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jalapeno Pepper - Fresh</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="E48" t="n">
+        <v>66.54000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NH166</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lettuce - Arcadian Blend</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FN108</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mango - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="E50" t="n">
+        <v>285.21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HB334</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Onion - Red Fresh Whole Peeled</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="E51" t="n">
+        <v>134.07</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>K7616</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Onion - Yellow (peeled)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>114.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VR126</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cheddar - Extra Sharp White</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PW962</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Smoked Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>570.08</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AV906</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Swiss (Sliced)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="E55" t="n">
+        <v>171.39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>W8538</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="E56" t="n">
+        <v>730.08</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J2280</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Yogurt - Plain (BIB)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="E57" t="n">
+        <v>87.15000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ABK44</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chicken Tenders - (1oz)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="E58" t="n">
+        <v>91.23999999999999</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GK608</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Corn - Frozen</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="E59" t="n">
+        <v>24.41</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A0280</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Edamame - FRZ Shelled</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="E60" t="n">
+        <v>44.16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>50778</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (Retail)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="E61" t="n">
+        <v>95.52</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LG162</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Base - Beef (No MSG)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="E62" t="n">
+        <v>46.81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>J3088</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Base - Chicken (No MSG)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="E63" t="n">
+        <v>62.49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ABK40</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chicken Wing - Fully Cooked</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>142.58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>142.58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CP992</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fries - Steak</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="E65" t="n">
+        <v>44.26</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P5596</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Haddock Fillet - Battered (frz)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="E66" t="n">
+        <v>232.04</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BL568</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pork Rib (St Louis Style)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FD046</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Potsticker - Chicken Lemongrass</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="E68" t="n">
+        <v>41.05</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BK482</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ravioli - Burrata</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="E69" t="n">
+        <v>89.08</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CK296</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Stuffed Shells</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="E70" t="n">
+        <v>97.54000000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NG746</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Wrap - Garlic Herb (12')</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="E71" t="n">
+        <v>29.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
